--- a/data/samples/external/nhsa/H-UDMP-SAMPLE-NHSA-DISABLED-v1.0.xlsx
+++ b/data/samples/external/nhsa/H-UDMP-SAMPLE-NHSA-DISABLED-v1.0.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>C03170208900004111100000209</t>
+          <t>C09100100000000211790000049</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -443,7 +443,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C03170208900004111100000210</t>
+          <t>C09100100000000211790000050</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -455,7 +455,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C03170208900004111100000211</t>
+          <t>C09100100000000211790000051</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -467,7 +467,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C03170208900004111100000212</t>
+          <t>C09100100000000211790000052</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -479,7 +479,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C03170208900004111100000213</t>
+          <t>C09100100000000211790000053</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -491,7 +491,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C03170208900004111100000214</t>
+          <t>C09100100000000211790000054</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -503,7 +503,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C03170208900004111100000215</t>
+          <t>C09100100000000211790000055</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -515,7 +515,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C03170208900004111100000216</t>
+          <t>C09100100000000211790000056</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -527,7 +527,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C03170208900004111100000217</t>
+          <t>C09100100000000211790000057</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -539,7 +539,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C03170208900004111100000218</t>
+          <t>C09100100000000211790000058</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -551,7 +551,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>C03170208900004111100000219</t>
+          <t>C09100100000000211790000059</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -563,7 +563,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>C03170208900004111100000220</t>
+          <t>C09100100000000211790000060</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
